--- a/apps/os-hub/public/idom-template.xlsx
+++ b/apps/os-hub/public/idom-template.xlsx
@@ -11,6 +11,7 @@
     <sheet name="עצמאים" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="חברות" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="מנהלים" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="הצהרות הון" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,14 +37,9 @@
     </font>
     <font>
       <name val="Heebo"/>
-      <color rgb="001B2A4A"/>
+      <i val="1"/>
+      <color rgb="000F1D35"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Heebo"/>
-      <i val="1"/>
-      <color rgb="001B2A4A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Heebo"/>
@@ -54,8 +50,13 @@
     <font>
       <name val="Heebo"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="005D6D7E"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Heebo"/>
+      <color rgb="000F1D35"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -67,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C5A572"/>
+        <fgColor rgb="00F8F7F4"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,11 +78,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F7F4"/>
+        <fgColor rgb="00F2EFE6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -89,28 +90,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5A572"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5A572"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5A572"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5A572"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -478,61 +487,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>הוראות שימוש — תבנית אידום</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>הוראות — תבנית IDOM (גרסת SHAAM אמיתית, 10 עמודות)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. להיכנס לשע"מ עם כרטיס חכם</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+          <t>1. גרסת SHAAM אמיתית — סדר העמודות זהה לפלט שאילתת מעקב דוחות:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. להריץ שאילתת מעקב דוחות</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3. סדר העמודות בתבנית זהה לסדר בשאילתא — אפשר להדביק ישירות החל משורה 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+          <t xml:space="preserve">   קוד שידור | תאריך ארכה | תאריך הגשה | מח | ס"ש | סוג תיק | ח | פקיד שומה | שם משפחה ופרטי | מספר תיק</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4. שנת מס לא צריכה להופיע בקובץ — נקבעת במסך ההרצה ב-OS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
+          <t>2. עמודות מיוחדות:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>5. עמודת "תאריך הגשה" ריקה משמעה: טרם הוגש</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+          <t xml:space="preserve">   • קוד שידור: 'MK' = הוגש באופן מקוון; ריק = טרם הוגש; ערכים אחרים אפשריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6. ת"ז / ח"פ של 9 ספרות — מפתח ההצלבה מול סאמיט</t>
+          <t xml:space="preserve">   • מח (מחוז): לרוב ריק בייצוא חדש — לא חוסם</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • ס"ש: שנת שומה פנימית של SHAAM, כמעט תמיד 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • ח: חוליה — תת־קבוצה תחת פקיד שומה (1-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3. הדבק את הנתונים החל משורה 5 (אחרי כותרות + רמזים)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>4. כל גליון ימופה לסוג דוח שונה: עצמאים → שנתיים, חברות → כספיים</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5. גליונות מנהלים / הצהרות הון יקראו אבל לא יסונכרנו (אין יעד ב-Summit עדיין)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6. שנת המס נקבעת ב-OS בעת ההעלאה — לא בקובץ.</t>
         </is>
       </c>
     </row>
@@ -547,110 +600,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>תבנית אידום — עצמאים | ביטן את ביטן</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>תבנית IDOM — עצמאים</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>להדביק נתונים מהשאילתא בשע"מ החל משורה 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>דוחות שנתיים — יחידים (עצמאים)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>קוד שידור</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>תאריך ארכה</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>תאריך הגשה</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>מח</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>ס'ש</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>סוג תיק</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ח</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>פקיד שומה</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>שם משפחה ופרטי</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>מספר תיק</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>תאריך הארכה</t>
+          <t>MK = הוגש מקוון / ריק = טרם</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>ריק = טרם הוגש</t>
+          <t>תאריך ארכה (DD/MM/YYYY)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>מחוז</t>
+          <t>תאריך הגשה — ריק אם טרם הוגש</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>קוד סוג תיק</t>
+          <t>מחוז (לרוב ריק בייצוא חדש)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>מספר פקיד שומה</t>
+          <t>שנת שומה SHAAM (0)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>שם מלא כפי שמופיע בשע"מ</t>
+          <t>42/52/94/96</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>ת"ז 9 ספרות / ח"פ 9 ספרות</t>
+          <t>חוליה — תת־קבוצה תחת פ.ש</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>פקיד שומה (מספר)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>שם משפחה ופרטי</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>מספר תיק (9 ספרות)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -662,110 +748,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>תבנית אידום — חברות | ביטן את ביטן</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>תבנית IDOM — חברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>להדביק נתונים מהשאילתא בשע"מ החל משורה 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>דוחות כספיים — חברות / שותפויות / נאמנויות</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>קוד שידור</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>תאריך ארכה</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>תאריך הגשה</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>מח</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>ס'ש</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>סוג תיק</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ח</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>פקיד שומה</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>שם משפחה ופרטי</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>מספר תיק</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>תאריך הארכה</t>
+          <t>MK = הוגש מקוון / ריק = טרם</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>ריק = טרם הוגש</t>
+          <t>תאריך ארכה (DD/MM/YYYY)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>מחוז</t>
+          <t>תאריך הגשה — ריק אם טרם הוגש</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>קוד סוג תיק</t>
+          <t>מחוז (לרוב ריק בייצוא חדש)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>מספר פקיד שומה</t>
+          <t>שנת שומה SHAAM (0)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>שם מלא כפי שמופיע בשע"מ</t>
+          <t>42/52/94/96</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>ת"ז 9 ספרות / ח"פ 9 ספרות</t>
+          <t>חוליה — תת־קבוצה תחת פ.ש</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>פקיד שומה (מספר)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>שם משפחה ופרטי</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>מספר תיק (9 ספרות)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -777,110 +896,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>תבנית אידום — מנהלים | ביטן את ביטן</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>תבנית IDOM — מנהלים</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>להדביק נתונים מהשאילתא בשע"מ החל משורה 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>מנהלים — לא ממופה ל-Summit עדיין, ינותח אך לא ייכתב</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>קוד שידור</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>תאריך ארכה</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>תאריך הגשה</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>מח</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>ס'ש</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>סוג תיק</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ח</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>פקיד שומה</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>שם משפחה ופרטי</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>מספר תיק</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>תאריך הארכה</t>
+          <t>MK = הוגש מקוון / ריק = טרם</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>ריק = טרם הוגש</t>
+          <t>תאריך ארכה (DD/MM/YYYY)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>מחוז</t>
+          <t>תאריך הגשה — ריק אם טרם הוגש</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>קוד סוג תיק</t>
+          <t>מחוז (לרוב ריק בייצוא חדש)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>מספר פקיד שומה</t>
+          <t>שנת שומה SHAAM (0)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>שם מלא כפי שמופיע בשע"מ</t>
+          <t>42/52/94/96</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>ת"ז 9 ספרות / ח"פ 9 ספרות</t>
+          <t>חוליה — תת־קבוצה תחת פ.ש</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>פקיד שומה (מספר)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>שם משפחה ופרטי</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>מספר תיק (9 ספרות)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>תבנית IDOM — הצהרות הון</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>הצהרות הון — לא ממופה ל-Summit עדיין</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>קוד שידור</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>תאריך ארכה</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>תאריך הגשה</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>מח</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>ס'ש</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>סוג תיק</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ח</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>פקיד שומה</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>שם משפחה ופרטי</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>מספר תיק</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MK = הוגש מקוון / ריק = טרם</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>תאריך ארכה (DD/MM/YYYY)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>תאריך הגשה — ריק אם טרם הוגש</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>מחוז (לרוב ריק בייצוא חדש)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>שנת שומה SHAAM (0)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>42/52/94/96</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>חוליה — תת־קבוצה תחת פ.ש</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>פקיד שומה (מספר)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>שם משפחה ופרטי</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>מספר תיק (9 ספרות)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
